--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_False.xlsx
@@ -34,85 +34,85 @@
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>10.57s (18.06 s)</t>
-  </si>
-  <si>
     <t>2.45 (1.97)</t>
   </si>
   <si>
+    <t>4.88s (20.34 s)</t>
+  </si>
+  <si>
     <t>89909.03 (70058.73 &gt; 28.65%)</t>
   </si>
   <si>
-    <t>2.05s (18.06 s)</t>
-  </si>
-  <si>
     <t>1.84 (1.97)</t>
   </si>
   <si>
+    <t>3.69s (20.34 s)</t>
+  </si>
+  <si>
     <t>72922.88 (70058.73 &gt; 3.93%)</t>
   </si>
   <si>
-    <t>14.76s (18.06 s)</t>
-  </si>
-  <si>
     <t>1.97 (1.97)</t>
   </si>
   <si>
+    <t>19.03s (20.34 s)</t>
+  </si>
+  <si>
     <t>70057.65 (70058.73 &gt; 0.01%)</t>
   </si>
   <si>
-    <t>9.24s (18.06 s)</t>
+    <t>12.37s (20.34 s)</t>
   </si>
 </sst>
 </file>
@@ -512,33 +512,33 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.06551670283079147</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="C3">
-        <v>0.0179436206817627</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="D3">
-        <v>0.006228530779480934</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="E3">
-        <v>0.006228530779480934</v>
+        <v>1.415648811724072E-16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>0.01823647692799568</v>
-      </c>
-      <c r="C4">
-        <v>0.006941535975784063</v>
-      </c>
-      <c r="D4">
-        <v>0.001363039249554276</v>
-      </c>
-      <c r="E4">
-        <v>0.001363039249554276</v>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -562,17 +562,17 @@
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
+      <c r="B6">
+        <v>0.02194234728813171</v>
+      </c>
+      <c r="C6">
+        <v>0.01904748566448689</v>
+      </c>
+      <c r="D6">
+        <v>0.00682216277346015</v>
+      </c>
+      <c r="E6">
+        <v>0.00682216277346015</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -580,16 +580,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.415648811724072E-16</v>
+        <v>0.01918262429535389</v>
       </c>
       <c r="C7">
-        <v>1.415648811724072E-16</v>
+        <v>0.0001790939859347418</v>
       </c>
       <c r="D7">
-        <v>1.415648811724072E-16</v>
+        <v>2.304499730598764E-06</v>
       </c>
       <c r="E7">
-        <v>1.415648811724072E-16</v>
+        <v>2.304499730598764E-06</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -614,50 +614,50 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>2.120720691379777E-17</v>
+        <v>0.2837492823600769</v>
       </c>
       <c r="C9">
-        <v>2.120720691379777E-17</v>
+        <v>0.005630467087030411</v>
       </c>
       <c r="D9">
-        <v>2.120720691379777E-17</v>
+        <v>2.60684646491427E-05</v>
       </c>
       <c r="E9">
-        <v>2.120720691379777E-17</v>
+        <v>2.60684646491427E-05</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>0.01918262429535389</v>
-      </c>
-      <c r="C10">
-        <v>0.0001790939859347418</v>
-      </c>
-      <c r="D10">
-        <v>2.304499730598764E-06</v>
-      </c>
-      <c r="E10">
-        <v>2.304499730598764E-06</v>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>0.04132245108485222</v>
-      </c>
-      <c r="C11">
-        <v>0.03525746986269951</v>
-      </c>
-      <c r="D11">
-        <v>0.007795904763042927</v>
-      </c>
-      <c r="E11">
-        <v>0.007795904763042927</v>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,16 +665,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>7.902863580966368E-05</v>
+        <v>0.000161314063007012</v>
       </c>
       <c r="C12">
-        <v>2.490309270797297E-05</v>
+        <v>2.789805512293242E-05</v>
       </c>
       <c r="D12">
-        <v>1.132073430198943E-05</v>
+        <v>1.056747805705527E-05</v>
       </c>
       <c r="E12">
-        <v>1.132073430198943E-05</v>
+        <v>1.056747805705527E-05</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +682,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.000161314063007012</v>
+        <v>0.01823647692799568</v>
       </c>
       <c r="C13">
-        <v>2.789805512293242E-05</v>
+        <v>0.006941535975784063</v>
       </c>
       <c r="D13">
-        <v>1.056747805705527E-05</v>
+        <v>0.001363039249554276</v>
       </c>
       <c r="E13">
-        <v>1.056747805705527E-05</v>
+        <v>0.001363039249554276</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,16 +699,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.01802909187972546</v>
+        <v>0.04132245108485222</v>
       </c>
       <c r="C14">
-        <v>0.006819524336606264</v>
+        <v>0.03525746986269951</v>
       </c>
       <c r="D14">
-        <v>0.001358434907160699</v>
+        <v>0.007795904763042927</v>
       </c>
       <c r="E14">
-        <v>0.001358434907160699</v>
+        <v>0.007795904763042927</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +716,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.02194234728813171</v>
+        <v>7.902863580966368E-05</v>
       </c>
       <c r="C15">
-        <v>0.01904748566448689</v>
+        <v>2.490309270797297E-05</v>
       </c>
       <c r="D15">
-        <v>0.00682216277346015</v>
+        <v>1.132073430198943E-05</v>
       </c>
       <c r="E15">
-        <v>0.00682216277346015</v>
+        <v>1.132073430198943E-05</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +733,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.2837492823600769</v>
+        <v>0.9270297288894653</v>
       </c>
       <c r="C16">
-        <v>0.005630467087030411</v>
+        <v>0.03568466752767563</v>
       </c>
       <c r="D16">
-        <v>2.60684646491427E-05</v>
+        <v>1.319911825703457E-05</v>
       </c>
       <c r="E16">
-        <v>2.60684646491427E-05</v>
+        <v>1.319911825703457E-05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,50 +750,50 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.9270297288894653</v>
+        <v>0.01802909187972546</v>
       </c>
       <c r="C17">
-        <v>0.03568466752767563</v>
+        <v>0.006819524336606264</v>
       </c>
       <c r="D17">
-        <v>1.319911825703457E-05</v>
+        <v>0.001358434907160699</v>
       </c>
       <c r="E17">
-        <v>1.319911825703457E-05</v>
+        <v>0.001358434907160699</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
+      <c r="B18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="C18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="D18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="E18">
+        <v>2.120720691379777E-17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
+      <c r="B19">
+        <v>0.06551670283079147</v>
+      </c>
+      <c r="C19">
+        <v>0.0179436206817627</v>
+      </c>
+      <c r="D19">
+        <v>0.006228530779480934</v>
+      </c>
+      <c r="E19">
+        <v>0.006228530779480934</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_False.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Pg Vm Projection False</t>
   </si>
@@ -31,88 +31,94 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
+    <t>Iinj_i_tot</t>
   </si>
   <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>2.45 (1.97)</t>
-  </si>
-  <si>
-    <t>4.88s (20.34 s)</t>
-  </si>
-  <si>
-    <t>89909.03 (70058.73 &gt; 28.65%)</t>
-  </si>
-  <si>
-    <t>1.84 (1.97)</t>
-  </si>
-  <si>
-    <t>3.69s (20.34 s)</t>
-  </si>
-  <si>
-    <t>72922.88 (70058.73 &gt; 3.93%)</t>
-  </si>
-  <si>
-    <t>1.97 (1.97)</t>
-  </si>
-  <si>
-    <t>19.03s (20.34 s)</t>
-  </si>
-  <si>
-    <t>70057.65 (70058.73 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>12.37s (20.34 s)</t>
+    <t>89901.44 (70031.70 &gt; 28.37%)</t>
+  </si>
+  <si>
+    <t>0.27s (0.32 s)</t>
+  </si>
+  <si>
+    <t>245.48 (195.70)</t>
+  </si>
+  <si>
+    <t>72957.87 (70130.05 &gt; 4.03%)</t>
+  </si>
+  <si>
+    <t>0.35s (0.32 s)</t>
+  </si>
+  <si>
+    <t>183.87 (197.84)</t>
+  </si>
+  <si>
+    <t>69989.69 (69989.84 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>0.33s (0.32 s)</t>
+  </si>
+  <si>
+    <t>195.69 (195.69)</t>
+  </si>
+  <si>
+    <t>70087.42 (70087.58 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>196.54 (196.54)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,50 +501,38 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.2974418997764587</v>
+        <v>0.9481443166732788</v>
       </c>
       <c r="C2">
-        <v>0.005853098351508379</v>
+        <v>0.05076460167765617</v>
       </c>
       <c r="D2">
-        <v>2.632787436596118E-05</v>
+        <v>0.02917762286961079</v>
       </c>
       <c r="E2">
-        <v>2.632787436596118E-05</v>
+        <v>0.02848604694008827</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="C3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="D3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="E3">
-        <v>1.415648811724072E-16</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.4513544142246246</v>
+      </c>
+      <c r="C4">
+        <v>0.0646066889166832</v>
+      </c>
+      <c r="D4">
+        <v>0.05549294874072075</v>
+      </c>
+      <c r="E4">
+        <v>0.05531441047787666</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -546,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.4307813346385956</v>
+        <v>0.01905393786728382</v>
       </c>
       <c r="C5">
-        <v>0.01673392578959465</v>
+        <v>0.01224617380648851</v>
       </c>
       <c r="D5">
-        <v>9.185793715005275E-06</v>
+        <v>0.004628929775208235</v>
       </c>
       <c r="E5">
-        <v>9.185793715005275E-06</v>
+        <v>0.004632360301911831</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +557,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.02194234728813171</v>
+        <v>0.000483393669128418</v>
       </c>
       <c r="C6">
-        <v>0.01904748566448689</v>
+        <v>0.0002235833235317841</v>
       </c>
       <c r="D6">
-        <v>0.00682216277346015</v>
+        <v>0.0002076638193102553</v>
       </c>
       <c r="E6">
-        <v>0.00682216277346015</v>
+        <v>0.0002095302479574457</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.01918262429535389</v>
-      </c>
-      <c r="C7">
-        <v>0.0001790939859347418</v>
-      </c>
-      <c r="D7">
-        <v>2.304499730598764E-06</v>
-      </c>
-      <c r="E7">
-        <v>2.304499730598764E-06</v>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,16 +591,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.3592671751976013</v>
+        <v>0.5746023058891296</v>
       </c>
       <c r="C8">
-        <v>0.01553153898566961</v>
+        <v>0.5704234838485718</v>
       </c>
       <c r="D8">
-        <v>9.123721247306094E-05</v>
+        <v>0.5680546164512634</v>
       </c>
       <c r="E8">
-        <v>9.123721247306094E-05</v>
+        <v>0.5695005059242249</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -614,33 +608,33 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.2837492823600769</v>
+        <v>0.08657832443714142</v>
       </c>
       <c r="C9">
-        <v>0.005630467087030411</v>
+        <v>0.0864795595407486</v>
       </c>
       <c r="D9">
-        <v>2.60684646491427E-05</v>
+        <v>0.08619318902492523</v>
       </c>
       <c r="E9">
-        <v>2.60684646491427E-05</v>
+        <v>0.08628851175308228</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
+      <c r="B10">
+        <v>0.02010029554367065</v>
+      </c>
+      <c r="C10">
+        <v>0.005110752768814564</v>
+      </c>
+      <c r="D10">
+        <v>0.005166520364582539</v>
+      </c>
+      <c r="E10">
+        <v>0.005166453775018454</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -665,16 +659,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.000161314063007012</v>
+        <v>0.3764025866985321</v>
       </c>
       <c r="C12">
-        <v>2.789805512293242E-05</v>
+        <v>0.0634566992521286</v>
       </c>
       <c r="D12">
-        <v>1.056747805705527E-05</v>
+        <v>0.05461154133081436</v>
       </c>
       <c r="E12">
-        <v>1.056747805705527E-05</v>
+        <v>0.05443347990512848</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +676,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01823647692799568</v>
+        <v>0.5535569190979004</v>
       </c>
       <c r="C13">
-        <v>0.006941535975784063</v>
+        <v>0.5496992468833923</v>
       </c>
       <c r="D13">
-        <v>0.001363039249554276</v>
+        <v>0.5473940968513489</v>
       </c>
       <c r="E13">
-        <v>0.001363039249554276</v>
+        <v>0.5487621426582336</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.04132245108485222</v>
+        <v>0.03688185662031174</v>
       </c>
       <c r="C14">
-        <v>0.03525746986269951</v>
+        <v>0.02772114984691143</v>
       </c>
       <c r="D14">
-        <v>0.007795904763042927</v>
+        <v>0.01158070098608732</v>
       </c>
       <c r="E14">
-        <v>0.007795904763042927</v>
+        <v>0.01155159901827574</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +710,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>7.902863580966368E-05</v>
+        <v>0.1003295406699181</v>
       </c>
       <c r="C15">
-        <v>2.490309270797297E-05</v>
+        <v>0.100064292550087</v>
       </c>
       <c r="D15">
-        <v>1.132073430198943E-05</v>
+        <v>0.09979095309972763</v>
       </c>
       <c r="E15">
-        <v>1.132073430198943E-05</v>
+        <v>0.09993746876716614</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +727,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.9270297288894653</v>
+        <v>0.004694301635026932</v>
       </c>
       <c r="C16">
-        <v>0.03568466752767563</v>
+        <v>0.004561653360724449</v>
       </c>
       <c r="D16">
-        <v>1.319911825703457E-05</v>
+        <v>0.004559707827866077</v>
       </c>
       <c r="E16">
-        <v>1.319911825703457E-05</v>
+        <v>0.004536266438663006</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,33 +744,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01802909187972546</v>
+        <v>0.0005632719257846475</v>
       </c>
       <c r="C17">
-        <v>0.006819524336606264</v>
+        <v>0.0005560330464504659</v>
       </c>
       <c r="D17">
-        <v>0.001358434907160699</v>
+        <v>0.0005539624835364521</v>
       </c>
       <c r="E17">
-        <v>0.001358434907160699</v>
+        <v>0.0005398106877692044</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="C18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="D18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="E18">
-        <v>2.120720691379777E-17</v>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +778,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.06551670283079147</v>
+        <v>0.06403734534978867</v>
       </c>
       <c r="C19">
-        <v>0.0179436206817627</v>
+        <v>0.01551750861108303</v>
       </c>
       <c r="D19">
-        <v>0.006228530779480934</v>
+        <v>0.008623755536973476</v>
       </c>
       <c r="E19">
-        <v>0.006228530779480934</v>
+        <v>0.008725200779736042</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.0005767736583948135</v>
+      </c>
+      <c r="C20">
+        <v>3.282334728282876E-05</v>
+      </c>
+      <c r="D20">
+        <v>1.363974570267601E-05</v>
+      </c>
+      <c r="E20">
+        <v>1.355203312414233E-05</v>
       </c>
     </row>
   </sheetData>
